--- a/agriculture 43.xlsx
+++ b/agriculture 43.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t xml:space="preserve">2017-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -251,7 +254,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -261,22 +263,36 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Footnote Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">: Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Footnote Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
   </si>
   <si>
     <t xml:space="preserve">1962-63 to 2013-14 - Plantation Crops: Coffee: Area:-&gt; Area refers to the total planted area.</t>
@@ -300,10 +316,25 @@
     <t xml:space="preserve">Plantation Crops: Coffee: Yield:-&gt; Coffee Yield is based on plucked area.</t>
   </si>
   <si>
-    <t xml:space="preserve">Discription:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Discription: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -314,7 +345,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -345,11 +376,28 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -415,7 +463,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -444,15 +492,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -473,8 +529,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14.42"/>
   </cols>
@@ -1420,89 +1476,154 @@
         <v>6.76461585552495</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8" t="s">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-    </row>
-    <row r="72" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="9" t="s">
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+    </row>
+    <row r="73" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+    </row>
+    <row r="74" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+    </row>
+    <row r="75" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+    </row>
+    <row r="76" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+    </row>
+    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+    </row>
+    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+    </row>
+    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+    </row>
+    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+    </row>
+    <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+    </row>
+    <row r="82" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="11" t="s">
         <v>86</v>
       </c>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
     </row>
     <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A83" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:E71"/>
+  <mergeCells count="13">
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A82:F82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 43.xlsx
+++ b/agriculture 43.xlsx
@@ -244,7 +244,7 @@
     <t xml:space="preserve">2017-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <r>
@@ -254,6 +254,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -263,6 +264,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF( Economic and Political Weekly Research Foundation) 1950-2020</t>
     </r>
@@ -275,6 +277,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Footnote Description: </t>
     </r>
@@ -284,6 +287,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Telangana:-&gt; On 2 June 2014, Telangana was separated from Andhra Pradesh as the 29th state of India. However Indian Horticulture Database disseminated separate data for both Andhra Pradesh &amp; Telangana in the year 2013-14</t>
     </r>
@@ -323,6 +327,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Discription: </t>
     </r>
@@ -332,6 +337,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -345,7 +351,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -376,28 +382,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -463,7 +459,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -492,23 +488,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -530,7 +522,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14.42"/>
   </cols>
@@ -1506,105 +1498,60 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="74" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-    </row>
-    <row r="75" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="75" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-    </row>
-    <row r="76" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="76" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-    </row>
-    <row r="77" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="77" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-    </row>
-    <row r="78" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="78" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-    </row>
-    <row r="79" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="79" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-    </row>
-    <row r="80" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-    </row>
-    <row r="81" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="81" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-    </row>
-    <row r="82" s="10" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
+    </row>
+    <row r="82" s="9" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>

--- a/agriculture 43.xlsx
+++ b/agriculture 43.xlsx
@@ -244,7 +244,7 @@
     <t xml:space="preserve">2017-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -522,7 +522,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14.42"/>
   </cols>
